--- a/originales/respuestas/2025/01. Calificadas/root/Fondo De Prestaciones Económicas, Cesantías Y Pensiones.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Fondo De Prestaciones Económicas, Cesantías Y Pensiones.xlsx
@@ -424,7 +424,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -5671,7 +5671,7 @@
       <c r="C18" s="11">
         <v>17.0</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="12" t="s">
         <v>130</v>
       </c>
       <c r="E18" s="10"/>
